--- a/2026/FMSys'26 Program.xlsx
+++ b/2026/FMSys'26 Program.xlsx
@@ -219,7 +219,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -312,6 +312,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -872,7 +875,7 @@
       <c r="D18" s="32" t="inlineStr">
         <is>
           <t>Speaker: Elisabetta Farella (FBK, Italy)
-Moderator: TBD</t>
+Moderator: Abbas Rahimi (IBM Zurich)</t>
         </is>
       </c>
     </row>
@@ -890,7 +893,7 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>Session Chair: TBD</t>
+          <t>Session Chair: Xiaomin Ouyang (HKUST)</t>
         </is>
       </c>
     </row>
@@ -987,42 +990,39 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Panel Discussion</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>Moderator: TBD</t>
+          <t>Panel Discussion: Where Shall We Go Next? Repositioning CPS/IoT Research in the Era of Foundation Models: Autonomy, Models, Safety, and Architectures</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>Panel Members: Tarek Abdelzaher (UIUC), Qian Zhang (HKUST), Samarjit Chakraborty (UNC Chapel Hill), Salma Elmalaki (University of California, Irvine), Shengzhong Liu (Shanghai Jiaotong University)
+Moderator: Xiaomin Ouyang (HKUST)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="29" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>Panel Members: TBD</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="n"/>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>17:15 - 17:30</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>Closing Remarks and Awards</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Abbas Rahimi (IBM Zurich), Stephen Xia (Northwestern University), Xiaomin Ouyang (HKUST)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="29" t="n"/>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>17:15 - 17:30</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>Closing Remarks and Awards</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>Abbas Rahimi (IBM Zurich), Stephen Xia (Northwestern University), Xiaomin Ouyang (HKUST)</t>
-        </is>
-      </c>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="26" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="33" t="n"/>

--- a/2026/FMSys'26 Program.xlsx
+++ b/2026/FMSys'26 Program.xlsx
@@ -623,12 +623,12 @@
       <c r="A2" s="29" t="n"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>Venue</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Lamainais 3 (Level 3)</t>
+          <t>Lamenais 3 (Level 3), Palais des Congrès de Saint Malo</t>
         </is>
       </c>
       <c r="D2" s="8" t="n"/>

--- a/2026/FMSys'26 Program.xlsx
+++ b/2026/FMSys'26 Program.xlsx
@@ -930,12 +930,12 @@
       <c r="B22" s="12" t="n"/>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>X-CPS: A Top-Down Hierarchical Framework for Explaining Learning-enabled Cyber-Physical Systems</t>
+          <t>Characterizing Cellular Network Dynamics for Federated Human Activity Recognition</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Guocheng He, Lingwen Deng, Ziyan An, Meiyi Ma (Vanderbilt University)</t>
+          <t>Muhammad Abdullah Soomro, Muhammad Shayan Nazeer, Taqi Raza, Fatima Anwar (University of Massachusetts Amherst)</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       <c r="B23" s="12" t="n"/>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>Characterizing Cellular Network Dynamics for Federated Human Activity Recognition</t>
+          <t>X-CPS: A Top-Down Hierarchical Framework for Explaining Learning-enabled Cyber-Physical Systems</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah Soomro, Muhammad Shayan Nazeer, Taqi Raza, Fatima Anwar (University of Massachusetts Amherst)</t>
+          <t>Guocheng He, Lingwen Deng, Ziyan An, Meiyi Ma (Vanderbilt University)</t>
         </is>
       </c>
     </row>
